--- a/FST16_Trash_Internal.xlsx
+++ b/FST16_Trash_Internal.xlsx
@@ -131,17 +131,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrashTable" displayName="TrashTable" ref="A1:H3" headerRowCount="1">
-  <autoFilter ref="A1:H3"/>
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrashTable" displayName="TrashTable" ref="A1:L19" headerRowCount="1">
+  <autoFilter ref="A1:L19"/>
+  <tableColumns count="12">
     <tableColumn id="1" name="Subassembly"/>
     <tableColumn id="2" name="Part Name"/>
     <tableColumn id="3" name="Version"/>
     <tableColumn id="4" name="Date"/>
     <tableColumn id="5" name="Weight (g)"/>
     <tableColumn id="6" name="Description"/>
-    <tableColumn id="7" name="Constraints"/>
+    <tableColumn id="7" name="Specifications"/>
     <tableColumn id="8" name="Image Path"/>
+    <tableColumn id="9" name="Stiffness Data"/>
+    <tableColumn id="10" name="LC Images"/>
+    <tableColumn id="11" name="Tolerancing Data"/>
+    <tableColumn id="12" name="Justification"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -436,17 +440,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,12 +490,32 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Constraints</t>
+          <t>Specifications</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
           <t>Image Path</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Stiffness Data</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>LC Images</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Tolerancing Data</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Justification</t>
         </is>
       </c>
     </row>
@@ -502,10 +530,8 @@
           <t>Transmission dummy</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="C2" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
@@ -518,32 +544,726 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>HB_02</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
+          <t>100X115X9 HMSA10 V1</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SKF Seal: 100X115X9 HMSA10 V1
+Datasheet: 100X115X9 </t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Inner D (mm): 100 | Outer D Min (mm): 115 | Width Min (mm): 8</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>105X130X12 HMSA10 V</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>SKF Seal: 105X130X12 HMSA10 V
+Datasheet: 105X130X12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Inner D (mm): 105 | Outer D Min (mm): 130 | Width Min (mm): 12</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>108X140X15 HMSA10 V</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SKF Seal: 108X140X15 HMSA10 V
+Datasheet: 108X140X15</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Inner D (mm): 108 | Outer D Min (mm): 140 | Width Min (mm): 15</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>110X130X8 HMSA10 V1</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SKF Seal: 110X130X8 HMSA10 V1
+Datasheet: 110X130X8 </t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Inner D (mm): 110 | Outer D Min (mm): 130 | Width Min (mm): 8</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>115X140X12 HMSA10 V</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SKF Seal: 115X140X12 HMSA10 V
+Datasheet: 115X140X12 </t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Inner D (mm): 115 | Outer D Min (mm): 140 | Width Min (mm): 12</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>120X140X12 HMSA10 V</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>SKF Seal: 120X140X12 HMSA10 V
+Datasheet: 120X140X12</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Inner D (mm): 120 | Outer D Min (mm): 140 | Width Min (mm): 12</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>61817</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>270</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Schaeffler Bearing: 61817
+Datasheet: 61817</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Inner D (mm): 85 | Dynamic Load Cr (kN): 20.4 | Static Load C0r (kN): 19.8 | Speed Limit (rpm): 8500</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>61818</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>287</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Schaeffler Bearing: 61818
+Datasheet: 61818</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Inner D (mm): 90 | Dynamic Load Cr (kN): 20.7 | Static Load C0r (kN): 20.6 | Speed Limit (rpm): 8100</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>61819</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>301</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Schaeffler Bearing: 61819
+Datasheet: 61819</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Inner D (mm): 95 | Dynamic Load Cr (kN): 21.0 | Static Load C0r (kN): 21.3 | Speed Limit (rpm): 7700</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>61820</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>315</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Schaeffler Bearing: 61820
+Datasheet: 61820</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Inner D (mm): 100 | Dynamic Load Cr (kN): 21.3 | Static Load C0r (kN): 22.1 | Speed Limit (rpm): 7400</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>61821</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>330</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Schaeffler Bearing: 61821
+Datasheet: 61821</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Inner D (mm): 105 | Dynamic Load Cr (kN): 22.1 | Static Load C0r (kN): 23.6 | Speed Limit (rpm): 7100</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>61822</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>509</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Schaeffler Bearing: 61822
+Datasheet: 61822</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Inner D (mm): 110 | Dynamic Load Cr (kN): 30.0 | Static Load C0r (kN): 30.5 | Speed Limit (rpm): 6500</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>61824</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>551</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Schaeffler Bearing: 61824
+Datasheet: 61824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Inner D (mm): 120 | Dynamic Load Cr (kN): 30.5 | Static Load C0r (kN): 33.0 | Speed Limit (rpm): 6100</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>71821-B-XL-TVP</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>316</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Schaeffler Bearing: 71821-B-XL-TVP
+Datasheet: 71821</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Inner D (mm): 105 | Dynamic Load Cr (kN): 24.7 | Static Load C0r (kN): 30.0 | Speed Limit (rpm): 6600</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>90X105X9 HMSA10 V1</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SKF Seal: 90X105X9 HMSA10 V1
+Datasheet: 90X105X9 </t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Inner D (mm): 90 | Outer D Min (mm): 105 | Width Min (mm): 9</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>UpperSupport Version</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:28:41</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-12 15:47:39</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">With all the features
+</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>images\UpperSupport Version_v1_0_imagem.png</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>{"load_case": "Wishbone Lateral 4.4 kN", "stress": 268.0, "yield_strength": 503.0, "sf": 1.88, "disp": 0.165, "material": "Al 7075-T6"}</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Clevis Pin Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (wishbone pin joint)"}, {"Interface / Feature": "Camber Shim Interface", "Nominal (mm)": "2 mm shims", "Fit / Tolerance": "+/- 0.02 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (camber adjustment +/- 0.5 deg)"}]</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Upper suspension wishbone mounting bracket interface to the upright body. Transmits camber and cornering suspension loads (up to 4.4 kN lateral) while permitting shim-based camber adjustment without remachining the upright body.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>UpperSupport Version</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:22:29</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Transmission: v2.0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>images/UpperSupport Version_v2_0_20261014_002229.png</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>{"load_case": "Wishbone Lateral 4.4 kN", "stress": 235.4, "yield_strength": 503.0, "sf": 2.14, "disp": 0.128, "material": "Al 7075-T6"}</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>[{"Interface / Feature": "Clevis Pin Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (wishbone pin joint)"}, {"Interface / Feature": "Camber Shim Interface", "Nominal (mm)": "2 mm shims", "Fit / Tolerance": "+/- 0.02 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (camber adjustment +/- 0.5 deg)"}]</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Upper suspension wishbone mounting bracket interface to the upright body. Transmits camber and cornering suspension loads (up to 4.4 kN lateral) while permitting shim-based camber adjustment without remachining the upright body.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/FST16_Trash_Internal.xlsx
+++ b/FST16_Trash_Internal.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,14 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -128,27 +122,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrashTable" displayName="TrashTable" ref="A1:L19" headerRowCount="1">
-  <autoFilter ref="A1:L19"/>
-  <tableColumns count="12">
-    <tableColumn id="1" name="Subassembly"/>
-    <tableColumn id="2" name="Part Name"/>
-    <tableColumn id="3" name="Version"/>
-    <tableColumn id="4" name="Date"/>
-    <tableColumn id="5" name="Weight (g)"/>
-    <tableColumn id="6" name="Description"/>
-    <tableColumn id="7" name="Specifications"/>
-    <tableColumn id="8" name="Image Path"/>
-    <tableColumn id="9" name="Stiffness Data"/>
-    <tableColumn id="10" name="LC Images"/>
-    <tableColumn id="11" name="Tolerancing Data"/>
-    <tableColumn id="12" name="Justification"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -442,20 +415,6 @@
   </sheetPr>
   <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="45" customWidth="1" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -520,746 +479,738 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Transmission dummy</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>2026-10-06 13:35:22</t>
         </is>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>100X115X9 HMSA10 V1</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>50</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">SKF Seal: 100X115X9 HMSA10 V1
 Datasheet: 100X115X9 </t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Inner D (mm): 100 | Outer D Min (mm): 115 | Width Min (mm): 8</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>105X130X12 HMSA10 V</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>102</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>SKF Seal: 105X130X12 HMSA10 V
 Datasheet: 105X130X12</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Inner D (mm): 105 | Outer D Min (mm): 130 | Width Min (mm): 12</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>108X140X15 HMSA10 V</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>123</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>SKF Seal: 108X140X15 HMSA10 V
 Datasheet: 108X140X15</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Inner D (mm): 108 | Outer D Min (mm): 140 | Width Min (mm): 15</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>110X130X8 HMSA10 V1</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>89.3</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t xml:space="preserve">SKF Seal: 110X130X8 HMSA10 V1
 Datasheet: 110X130X8 </t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Inner D (mm): 110 | Outer D Min (mm): 130 | Width Min (mm): 8</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>115X140X12 HMSA10 V</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>108</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t xml:space="preserve">SKF Seal: 115X140X12 HMSA10 V
 Datasheet: 115X140X12 </t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Inner D (mm): 115 | Outer D Min (mm): 140 | Width Min (mm): 12</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>120X140X12 HMSA10 V</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>103</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>SKF Seal: 120X140X12 HMSA10 V
 Datasheet: 120X140X12</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Inner D (mm): 120 | Outer D Min (mm): 140 | Width Min (mm): 12</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>61817</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>270</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61817
 Datasheet: 61817</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Inner D (mm): 85 | Dynamic Load Cr (kN): 20.4 | Static Load C0r (kN): 19.8 | Speed Limit (rpm): 8500</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>61818</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>287</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61818
 Datasheet: 61818</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Inner D (mm): 90 | Dynamic Load Cr (kN): 20.7 | Static Load C0r (kN): 20.6 | Speed Limit (rpm): 8100</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>61819</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>301</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61819
 Datasheet: 61819</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Inner D (mm): 95 | Dynamic Load Cr (kN): 21.0 | Static Load C0r (kN): 21.3 | Speed Limit (rpm): 7700</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>61820</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>315</v>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61820
 Datasheet: 61820</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Inner D (mm): 100 | Dynamic Load Cr (kN): 21.3 | Static Load C0r (kN): 22.1 | Speed Limit (rpm): 7400</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>61821</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>330</v>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61821
 Datasheet: 61821</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Inner D (mm): 105 | Dynamic Load Cr (kN): 22.1 | Static Load C0r (kN): 23.6 | Speed Limit (rpm): 7100</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>61822</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>509</v>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61822
 Datasheet: 61822</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Inner D (mm): 110 | Dynamic Load Cr (kN): 30.0 | Static Load C0r (kN): 30.5 | Speed Limit (rpm): 6500</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>61824</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>551</v>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61824
 Datasheet: 61824</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Inner D (mm): 120 | Dynamic Load Cr (kN): 30.5 | Static Load C0r (kN): 33.0 | Speed Limit (rpm): 6100</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>71821-B-XL-TVP</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
         <v>316</v>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 71821-B-XL-TVP
 Datasheet: 71821</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Inner D (mm): 105 | Dynamic Load Cr (kN): 24.7 | Static Load C0r (kN): 30.0 | Speed Limit (rpm): 6600</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>90X105X9 HMSA10 V1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
         <v>40</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t xml:space="preserve">SKF Seal: 90X105X9 HMSA10 V1
 Datasheet: 90X105X9 </t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Inner D (mm): 90 | Outer D Min (mm): 105 | Width Min (mm): 9</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>UpperSupport Version</t>
         </is>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>2026-10-12 15:47:39</t>
         </is>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" t="n">
         <v>112.5</v>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t xml:space="preserve">With all the features
 </t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
         <is>
           <t>images\UpperSupport Version_v1_0_imagem.png</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>{"load_case": "Wishbone Lateral 4.4 kN", "stress": 268.0, "yield_strength": 503.0, "sf": 1.88, "disp": 0.165, "material": "Al 7075-T6"}</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Clevis Pin Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (wishbone pin joint)"}, {"Interface / Feature": "Camber Shim Interface", "Nominal (mm)": "2 mm shims", "Fit / Tolerance": "+/- 0.02 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (camber adjustment +/- 0.5 deg)"}]</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>Upper suspension wishbone mounting bracket interface to the upright body. Transmits camber and cornering suspension loads (up to 4.4 kN lateral) while permitting shim-based camber adjustment without remachining the upright body.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>UpperSupport Version</t>
         </is>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>2026-10-14 00:22:29</t>
         </is>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E19" t="n">
         <v>98.2</v>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>images/UpperSupport Version_v2_0_20261014_002229.png</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>{"load_case": "Wishbone Lateral 4.4 kN", "stress": 235.4, "yield_strength": 503.0, "sf": 2.14, "disp": 0.128, "material": "Al 7075-T6"}</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>[{"Interface / Feature": "Clevis Pin Bore", "Nominal (mm)": "8", "Fit / Tolerance": "H7 (+0.015 / 0 mm)", "Roughness / Notes": "Ra &lt;= 0.8 um (wishbone pin joint)"}, {"Interface / Feature": "Camber Shim Interface", "Nominal (mm)": "2 mm shims", "Fit / Tolerance": "+/- 0.02 mm", "Roughness / Notes": "Ra &lt;= 1.6 um (camber adjustment +/- 0.5 deg)"}]</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>Upper suspension wishbone mounting bracket interface to the upright body. Transmits camber and cornering suspension loads (up to 4.4 kN lateral) while permitting shim-based camber adjustment without remachining the upright body.</t>
         </is>
@@ -1267,8 +1218,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/FST16_Trash_Internal.xlsx
+++ b/FST16_Trash_Internal.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,8 +46,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -122,6 +128,27 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TrashTable" displayName="TrashTable" ref="A1:L19" headerRowCount="1">
+  <autoFilter ref="A1:L19"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="Subassembly"/>
+    <tableColumn id="2" name="Part Name"/>
+    <tableColumn id="3" name="Version"/>
+    <tableColumn id="4" name="Date"/>
+    <tableColumn id="5" name="Weight (g)"/>
+    <tableColumn id="6" name="Description"/>
+    <tableColumn id="7" name="Specifications"/>
+    <tableColumn id="8" name="Image Path"/>
+    <tableColumn id="9" name="Stiffness Data"/>
+    <tableColumn id="10" name="LC Images"/>
+    <tableColumn id="11" name="Tolerancing Data"/>
+    <tableColumn id="12" name="Justification"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -415,6 +442,20 @@
   </sheetPr>
   <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -479,738 +520,738 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Transmission dummy</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>2026-10-06 13:35:22</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>100X115X9 HMSA10 V1</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SKF Seal: 100X115X9 HMSA10 V1
 Datasheet: 100X115X9 </t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 100 | Outer D Min (mm): 115 | Width Min (mm): 8</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>105X130X12 HMSA10 V</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>SKF Seal: 105X130X12 HMSA10 V
 Datasheet: 105X130X12</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 105 | Outer D Min (mm): 130 | Width Min (mm): 12</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>108X140X15 HMSA10 V</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>123</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>SKF Seal: 108X140X15 HMSA10 V
 Datasheet: 108X140X15</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 108 | Outer D Min (mm): 140 | Width Min (mm): 15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>110X130X8 HMSA10 V1</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>89.3</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SKF Seal: 110X130X8 HMSA10 V1
 Datasheet: 110X130X8 </t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 110 | Outer D Min (mm): 130 | Width Min (mm): 8</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>115X140X12 HMSA10 V</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SKF Seal: 115X140X12 HMSA10 V
 Datasheet: 115X140X12 </t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 115 | Outer D Min (mm): 140 | Width Min (mm): 12</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>120X140X12 HMSA10 V</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>SKF Seal: 120X140X12 HMSA10 V
 Datasheet: 120X140X12</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 120 | Outer D Min (mm): 140 | Width Min (mm): 12</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>61817</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="n">
         <v>270</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61817
 Datasheet: 61817</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 85 | Dynamic Load Cr (kN): 20.4 | Static Load C0r (kN): 19.8 | Speed Limit (rpm): 8500</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
         <is>
           <t>61818</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="n">
         <v>287</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61818
 Datasheet: 61818</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 90 | Dynamic Load Cr (kN): 20.7 | Static Load C0r (kN): 20.6 | Speed Limit (rpm): 8100</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>61819</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="n">
         <v>301</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61819
 Datasheet: 61819</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 95 | Dynamic Load Cr (kN): 21.0 | Static Load C0r (kN): 21.3 | Speed Limit (rpm): 7700</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>61820</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="n">
         <v>315</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61820
 Datasheet: 61820</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 100 | Dynamic Load Cr (kN): 21.3 | Static Load C0r (kN): 22.1 | Speed Limit (rpm): 7400</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
         <is>
           <t>61821</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="n">
         <v>330</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61821
 Datasheet: 61821</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 105 | Dynamic Load Cr (kN): 22.1 | Static Load C0r (kN): 23.6 | Speed Limit (rpm): 7100</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>61822</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="n">
         <v>509</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61822
 Datasheet: 61822</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 110 | Dynamic Load Cr (kN): 30.0 | Static Load C0r (kN): 30.5 | Speed Limit (rpm): 6500</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>61824</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="n">
         <v>551</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 61824
 Datasheet: 61824</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 120 | Dynamic Load Cr (kN): 30.5 | Static Load C0r (kN): 33.0 | Speed Limit (rpm): 6100</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>71821-B-XL-TVP</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="n">
         <v>316</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Schaeffler Bearing: 71821-B-XL-TVP
 Datasheet: 71821</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 105 | Dynamic Load Cr (kN): 24.7 | Static Load C0r (kN): 30.0 | Speed Limit (rpm): 6600</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>90X105X9 HMSA10 V1</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-10-06 11:00:06</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:00:06</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SKF Seal: 90X105X9 HMSA10 V1
 Datasheet: 90X105X9 </t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Inner D (mm): 90 | Outer D Min (mm): 105 | Width Min (mm): 9</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>UpperSupport Version</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="1" t="inlineStr">
         <is>
           <t>2026-10-12 15:47:39</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="1" t="n">
         <v>112.5</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">With all the features
 </t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>images\UpperSupport Version_v1_0_imagem.png</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>{"load_case": "Wishbone Lateral 4.4 kN", "stress": 268.0, "yield_strength": 503.0, "sf": 1.88, "disp": 0.165, "material": "Al 7075-T6"}</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Upper suspension wishbone mounting bracket interface to the upright body. Transmits camber and cornering suspension loads (up to 4.4 kN lateral) while permitting shim-based camber adjustment without remachining the upright body.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>UP</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>UpperSupport Version</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>2026-10-14 00:22:29</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="1" t="n">
         <v>98.2</v>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Transmission: v2.0</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>images/UpperSupport Version_v2_0_20261014_002229.png</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>{"load_case": "Wishbone Lateral 4.4 kN", "stress": 235.4, "yield_strength": 503.0, "sf": 2.14, "disp": 0.128, "material": "Al 7075-T6"}</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Upper suspension wishbone mounting bracket interface to the upright body. Transmits camber and cornering suspension loads (up to 4.4 kN lateral) while permitting shim-based camber adjustment without remachining the upright body.</t>
         </is>
@@ -1218,5 +1259,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>